--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/01004T-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/01004T-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93E62DED-BFB7-4B2E-AB17-7FC417F6E709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01F751C1-EDCF-4436-9477-657224E84C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D5F67AE5-AA78-4D16-9043-0713702AFC25}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{9B9EC556-980A-4CAB-94D0-E3F54C72EF22}"/>
   </bookViews>
   <sheets>
     <sheet name="01004T-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1598,25 +1598,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A322147-6706-49C7-A661-6D2B99789C42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E72CF4-73E2-4BD4-8B38-42EE4967351B}">
   <dimension ref="A1:R62"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1644,7 +1644,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1674,7 +1674,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1770,7 +1770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2018</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>25</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>25</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2017</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2016</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2015</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2014</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>25</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>25</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2013</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>25</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>25</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2012</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>25</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>25</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2011</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>25</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>25</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>2010</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>25</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
         <v>25</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>2009</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>25</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>25</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>2008</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
         <v>25</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
         <v>25</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="37">
         <v>2007</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>25</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>25</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="39" t="s">
         <v>85</v>
       </c>
